--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>136859533</v>
       </c>
       <c r="B119" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>136859549</v>
       </c>
       <c r="B120" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>136859565</v>
       </c>
       <c r="B121" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>136859571</v>
       </c>
       <c r="B122" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>136859585</v>
       </c>
       <c r="B123" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>136859467</v>
       </c>
       <c r="B124" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>136859471</v>
       </c>
       <c r="B125" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>136859474</v>
       </c>
       <c r="B126" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>136859478</v>
       </c>
       <c r="B127" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>136859492</v>
       </c>
       <c r="B128" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>136859499</v>
       </c>
       <c r="B129" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>136859508</v>
       </c>
       <c r="B130" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>136859509</v>
       </c>
       <c r="B131" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>136859510</v>
       </c>
       <c r="B132" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>136859511</v>
       </c>
       <c r="B133" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>136859514</v>
       </c>
       <c r="B134" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>136859520</v>
       </c>
       <c r="B135" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>136859521</v>
       </c>
       <c r="B136" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136859529</v>
       </c>
       <c r="B137" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>136859530</v>
       </c>
       <c r="B138" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>136859532</v>
       </c>
       <c r="B139" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>136859536</v>
       </c>
       <c r="B140" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>136859539</v>
       </c>
       <c r="B141" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>136859544</v>
       </c>
       <c r="B142" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>136859547</v>
       </c>
       <c r="B143" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>136859550</v>
       </c>
       <c r="B144" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>136859555</v>
       </c>
       <c r="B145" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>136859560</v>
       </c>
       <c r="B146" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>136859561</v>
       </c>
       <c r="B147" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>136859563</v>
       </c>
       <c r="B148" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136859576</v>
       </c>
       <c r="B149" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>136859581</v>
       </c>
       <c r="B150" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>136859591</v>
       </c>
       <c r="B151" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>136859592</v>
       </c>
       <c r="B152" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>136860253</v>
       </c>
       <c r="B153" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>136860257</v>
       </c>
       <c r="B154" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>136860260</v>
       </c>
       <c r="B155" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>136860265</v>
       </c>
       <c r="B156" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>136860275</v>
       </c>
       <c r="B157" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>136860278</v>
       </c>
       <c r="B158" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>136860283</v>
       </c>
       <c r="B159" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>136860286</v>
       </c>
       <c r="B160" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>136859464</v>
       </c>
       <c r="B161" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>136859582</v>
       </c>
       <c r="B162" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>136859546</v>
       </c>
       <c r="B167" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>136859517</v>
       </c>
       <c r="B168" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>136859588</v>
       </c>
       <c r="B169" t="n">
-        <v>58667</v>
+        <v>58680</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>136859533</v>
       </c>
       <c r="B119" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>136859549</v>
       </c>
       <c r="B120" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14473,7 +14473,7 @@
         <v>136859565</v>
       </c>
       <c r="B121" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14590,7 +14590,7 @@
         <v>136859571</v>
       </c>
       <c r="B122" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -14707,7 +14707,7 @@
         <v>136859585</v>
       </c>
       <c r="B123" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -14829,7 +14829,7 @@
         <v>136859467</v>
       </c>
       <c r="B124" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>136859471</v>
       </c>
       <c r="B125" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>136859474</v>
       </c>
       <c r="B126" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>136859478</v>
       </c>
       <c r="B127" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>136859492</v>
       </c>
       <c r="B128" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -15414,7 +15414,7 @@
         <v>136859499</v>
       </c>
       <c r="B129" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>136859508</v>
       </c>
       <c r="B130" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -15648,7 +15648,7 @@
         <v>136859509</v>
       </c>
       <c r="B131" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>136859510</v>
       </c>
       <c r="B132" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>136859511</v>
       </c>
       <c r="B133" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15999,7 +15999,7 @@
         <v>136859514</v>
       </c>
       <c r="B134" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>136859520</v>
       </c>
       <c r="B135" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -16233,7 +16233,7 @@
         <v>136859521</v>
       </c>
       <c r="B136" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136859529</v>
       </c>
       <c r="B137" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16467,7 +16467,7 @@
         <v>136859530</v>
       </c>
       <c r="B138" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16584,7 +16584,7 @@
         <v>136859532</v>
       </c>
       <c r="B139" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16701,7 +16701,7 @@
         <v>136859536</v>
       </c>
       <c r="B140" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16818,7 +16818,7 @@
         <v>136859539</v>
       </c>
       <c r="B141" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -16935,7 +16935,7 @@
         <v>136859544</v>
       </c>
       <c r="B142" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -17052,7 +17052,7 @@
         <v>136859547</v>
       </c>
       <c r="B143" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -17169,7 +17169,7 @@
         <v>136859550</v>
       </c>
       <c r="B144" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -17286,7 +17286,7 @@
         <v>136859555</v>
       </c>
       <c r="B145" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -17403,7 +17403,7 @@
         <v>136859560</v>
       </c>
       <c r="B146" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -17520,7 +17520,7 @@
         <v>136859561</v>
       </c>
       <c r="B147" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -17637,7 +17637,7 @@
         <v>136859563</v>
       </c>
       <c r="B148" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -17754,7 +17754,7 @@
         <v>136859576</v>
       </c>
       <c r="B149" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -17871,7 +17871,7 @@
         <v>136859581</v>
       </c>
       <c r="B150" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -17988,7 +17988,7 @@
         <v>136859591</v>
       </c>
       <c r="B151" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -18105,7 +18105,7 @@
         <v>136859592</v>
       </c>
       <c r="B152" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -18222,7 +18222,7 @@
         <v>136860253</v>
       </c>
       <c r="B153" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>136860257</v>
       </c>
       <c r="B154" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>136860260</v>
       </c>
       <c r="B155" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>136860265</v>
       </c>
       <c r="B156" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>136860275</v>
       </c>
       <c r="B157" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>136860278</v>
       </c>
       <c r="B158" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>136860283</v>
       </c>
       <c r="B159" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>136860286</v>
       </c>
       <c r="B160" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>136859464</v>
       </c>
       <c r="B161" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>136859582</v>
       </c>
       <c r="B162" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -19733,7 +19733,7 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -19850,7 +19850,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -19865,7 +19865,7 @@
         <v>136859546</v>
       </c>
       <c r="B167" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -19977,7 +19977,7 @@
         <v>136859517</v>
       </c>
       <c r="B168" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>136859588</v>
       </c>
       <c r="B169" t="n">
-        <v>58680</v>
+        <v>58682</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -20206,7 +20206,7 @@
         <v>136859481</v>
       </c>
       <c r="B170" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -20444,7 +20444,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -20677,7 +20677,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -20789,7 +20789,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -20901,7 +20901,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
@@ -21125,7 +21125,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -14265,11 +14265,7 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -14382,11 +14378,7 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -14499,11 +14491,7 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -14616,11 +14604,7 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -14733,11 +14717,7 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -14855,11 +14835,7 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -14972,11 +14948,7 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -15089,11 +15061,7 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -15206,11 +15174,7 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -15323,11 +15287,7 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -15440,11 +15400,7 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -15557,11 +15513,7 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -15674,11 +15626,7 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -15791,11 +15739,7 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -15908,11 +15852,7 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -16025,11 +15965,7 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -16142,11 +16078,7 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -16259,11 +16191,7 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -16376,11 +16304,7 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -16493,11 +16417,7 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -16610,11 +16530,7 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -16727,11 +16643,7 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -16844,11 +16756,7 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -17078,11 +16986,7 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -17195,11 +17099,7 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -17312,11 +17212,7 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -17429,11 +17325,7 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -17546,11 +17438,7 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -17663,11 +17551,7 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -17780,11 +17664,7 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -17897,11 +17777,7 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -18014,11 +17890,7 @@
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -18131,11 +18003,7 @@
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -18248,11 +18116,7 @@
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Manperstjärn, Dlr</t>
@@ -18370,11 +18234,7 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Manperstjärn, Dlr</t>
@@ -18487,11 +18347,7 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Manperstjärn, Dlr</t>
@@ -18604,11 +18460,7 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Manperstjärn, Dlr</t>
@@ -18721,11 +18573,7 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Manperstjärn, Dlr</t>
@@ -18838,11 +18686,7 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Manperstjärn, Dlr</t>
@@ -18955,11 +18799,7 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Manperstjärn, Dlr</t>
@@ -19072,11 +18912,7 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Manperstjärn, Dlr</t>
@@ -19189,11 +19025,7 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -19423,11 +19255,7 @@
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -19540,11 +19368,7 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -19657,11 +19481,7 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -19774,11 +19594,7 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -20003,11 +19819,7 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>
@@ -20232,11 +20044,7 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Manspertjärnen, Dlr</t>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14676,7 +14676,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -17397,7 +17397,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -19778,7 +19778,7 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -20003,7 +20003,7 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -20131,7 +20131,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -20252,7 +20252,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -20485,7 +20485,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>136859533</v>
       </c>
       <c r="B119" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>136859549</v>
       </c>
       <c r="B120" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>136859565</v>
       </c>
       <c r="B121" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>136859571</v>
       </c>
       <c r="B122" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>136859585</v>
       </c>
       <c r="B123" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>136859467</v>
       </c>
       <c r="B124" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>136859471</v>
       </c>
       <c r="B125" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>136859474</v>
       </c>
       <c r="B126" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>136859478</v>
       </c>
       <c r="B127" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>136859492</v>
       </c>
       <c r="B128" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>136859499</v>
       </c>
       <c r="B129" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>136859508</v>
       </c>
       <c r="B130" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>136859509</v>
       </c>
       <c r="B131" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>136859510</v>
       </c>
       <c r="B132" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136859511</v>
       </c>
       <c r="B133" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>136859514</v>
       </c>
       <c r="B134" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>136859520</v>
       </c>
       <c r="B135" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>136859521</v>
       </c>
       <c r="B136" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>136859529</v>
       </c>
       <c r="B137" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>136859530</v>
       </c>
       <c r="B138" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>136859532</v>
       </c>
       <c r="B139" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>136859536</v>
       </c>
       <c r="B140" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>136859539</v>
       </c>
       <c r="B141" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>136859544</v>
       </c>
       <c r="B142" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>136859547</v>
       </c>
       <c r="B143" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>136859550</v>
       </c>
       <c r="B144" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>136859555</v>
       </c>
       <c r="B145" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>136859560</v>
       </c>
       <c r="B146" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>136859561</v>
       </c>
       <c r="B147" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>136859563</v>
       </c>
       <c r="B148" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>136859576</v>
       </c>
       <c r="B149" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>136859581</v>
       </c>
       <c r="B150" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>136859591</v>
       </c>
       <c r="B151" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>136859592</v>
       </c>
       <c r="B152" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>136860253</v>
       </c>
       <c r="B153" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>136860257</v>
       </c>
       <c r="B154" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>136860260</v>
       </c>
       <c r="B155" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>136860265</v>
       </c>
       <c r="B156" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         <v>136860275</v>
       </c>
       <c r="B157" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>136860278</v>
       </c>
       <c r="B158" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>136860283</v>
       </c>
       <c r="B159" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>136860286</v>
       </c>
       <c r="B160" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>136859464</v>
       </c>
       <c r="B161" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>136859582</v>
       </c>
       <c r="B162" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>136859465</v>
       </c>
       <c r="B163" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>136859566</v>
       </c>
       <c r="B164" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>136859569</v>
       </c>
       <c r="B165" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>136859578</v>
       </c>
       <c r="B166" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>136859546</v>
       </c>
       <c r="B167" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>136859517</v>
       </c>
       <c r="B168" t="n">
-        <v>58644</v>
+        <v>58654</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136859588</v>
       </c>
       <c r="B169" t="n">
-        <v>58682</v>
+        <v>58692</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>136859481</v>
       </c>
       <c r="B170" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>136859533</v>
       </c>
       <c r="B119" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>136859549</v>
       </c>
       <c r="B120" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>136859565</v>
       </c>
       <c r="B121" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>136859571</v>
       </c>
       <c r="B122" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>136859585</v>
       </c>
       <c r="B123" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>136859467</v>
       </c>
       <c r="B124" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>136859471</v>
       </c>
       <c r="B125" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>136859474</v>
       </c>
       <c r="B126" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>136859478</v>
       </c>
       <c r="B127" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>136859492</v>
       </c>
       <c r="B128" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>136859499</v>
       </c>
       <c r="B129" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>136859508</v>
       </c>
       <c r="B130" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>136859509</v>
       </c>
       <c r="B131" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>136859510</v>
       </c>
       <c r="B132" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136859511</v>
       </c>
       <c r="B133" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>136859514</v>
       </c>
       <c r="B134" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>136859520</v>
       </c>
       <c r="B135" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>136859521</v>
       </c>
       <c r="B136" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>136859529</v>
       </c>
       <c r="B137" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>136859530</v>
       </c>
       <c r="B138" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>136859532</v>
       </c>
       <c r="B139" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>136859536</v>
       </c>
       <c r="B140" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>136859539</v>
       </c>
       <c r="B141" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>136859544</v>
       </c>
       <c r="B142" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>136859547</v>
       </c>
       <c r="B143" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>136859550</v>
       </c>
       <c r="B144" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>136859555</v>
       </c>
       <c r="B145" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>136859560</v>
       </c>
       <c r="B146" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>136859561</v>
       </c>
       <c r="B147" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>136859563</v>
       </c>
       <c r="B148" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>136859576</v>
       </c>
       <c r="B149" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>136859581</v>
       </c>
       <c r="B150" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>136859591</v>
       </c>
       <c r="B151" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>136859592</v>
       </c>
       <c r="B152" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>136860253</v>
       </c>
       <c r="B153" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>136860257</v>
       </c>
       <c r="B154" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>136860260</v>
       </c>
       <c r="B155" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>136860265</v>
       </c>
       <c r="B156" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         <v>136860275</v>
       </c>
       <c r="B157" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>136860278</v>
       </c>
       <c r="B158" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>136860283</v>
       </c>
       <c r="B159" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>136860286</v>
       </c>
       <c r="B160" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>136859464</v>
       </c>
       <c r="B161" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>136859582</v>
       </c>
       <c r="B162" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>136859546</v>
       </c>
       <c r="B167" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>136859517</v>
       </c>
       <c r="B168" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136859588</v>
       </c>
       <c r="B169" t="n">
-        <v>58692</v>
+        <v>58694</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>136859533</v>
       </c>
       <c r="B119" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>136859549</v>
       </c>
       <c r="B120" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>136859565</v>
       </c>
       <c r="B121" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>136859571</v>
       </c>
       <c r="B122" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>136859585</v>
       </c>
       <c r="B123" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>136859467</v>
       </c>
       <c r="B124" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>136859471</v>
       </c>
       <c r="B125" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>136859474</v>
       </c>
       <c r="B126" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>136859478</v>
       </c>
       <c r="B127" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>136859492</v>
       </c>
       <c r="B128" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>136859499</v>
       </c>
       <c r="B129" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>136859508</v>
       </c>
       <c r="B130" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>136859509</v>
       </c>
       <c r="B131" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>136859510</v>
       </c>
       <c r="B132" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136859511</v>
       </c>
       <c r="B133" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>136859514</v>
       </c>
       <c r="B134" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>136859520</v>
       </c>
       <c r="B135" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>136859521</v>
       </c>
       <c r="B136" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>136859529</v>
       </c>
       <c r="B137" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>136859530</v>
       </c>
       <c r="B138" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>136859532</v>
       </c>
       <c r="B139" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>136859536</v>
       </c>
       <c r="B140" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>136859539</v>
       </c>
       <c r="B141" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>136859544</v>
       </c>
       <c r="B142" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>136859547</v>
       </c>
       <c r="B143" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>136859550</v>
       </c>
       <c r="B144" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>136859555</v>
       </c>
       <c r="B145" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>136859560</v>
       </c>
       <c r="B146" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>136859561</v>
       </c>
       <c r="B147" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>136859563</v>
       </c>
       <c r="B148" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>136859576</v>
       </c>
       <c r="B149" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>136859581</v>
       </c>
       <c r="B150" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>136859591</v>
       </c>
       <c r="B151" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>136859592</v>
       </c>
       <c r="B152" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>136860253</v>
       </c>
       <c r="B153" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>136860257</v>
       </c>
       <c r="B154" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>136860260</v>
       </c>
       <c r="B155" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>136860265</v>
       </c>
       <c r="B156" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         <v>136860275</v>
       </c>
       <c r="B157" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>136860278</v>
       </c>
       <c r="B158" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>136860283</v>
       </c>
       <c r="B159" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>136860286</v>
       </c>
       <c r="B160" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>136859546</v>
       </c>
       <c r="B167" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>136859517</v>
       </c>
       <c r="B168" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136859588</v>
       </c>
       <c r="B169" t="n">
-        <v>58694</v>
+        <v>58696</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>

--- a/artfynd/A 37572-2026 artfynd.xlsx
+++ b/artfynd/A 37572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859434</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859436</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136859437</v>
       </c>
       <c r="B4" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136859438</v>
       </c>
       <c r="B5" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136859441</v>
       </c>
       <c r="B6" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136859442</v>
       </c>
       <c r="B7" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136859446</v>
       </c>
       <c r="B8" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136859454</v>
       </c>
       <c r="B9" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136859456</v>
       </c>
       <c r="B10" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136859458</v>
       </c>
       <c r="B11" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136859462</v>
       </c>
       <c r="B12" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136859469</v>
       </c>
       <c r="B13" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136859473</v>
       </c>
       <c r="B14" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136859476</v>
       </c>
       <c r="B15" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136859485</v>
       </c>
       <c r="B16" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136859489</v>
       </c>
       <c r="B17" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136859501</v>
       </c>
       <c r="B18" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136859512</v>
       </c>
       <c r="B19" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136859543</v>
       </c>
       <c r="B20" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136859558</v>
       </c>
       <c r="B21" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136859568</v>
       </c>
       <c r="B22" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136859584</v>
       </c>
       <c r="B23" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>136860251</v>
       </c>
       <c r="B24" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>136860256</v>
       </c>
       <c r="B25" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>136860259</v>
       </c>
       <c r="B26" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>136860268</v>
       </c>
       <c r="B27" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>136860280</v>
       </c>
       <c r="B28" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>136860290</v>
       </c>
       <c r="B29" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>136860295</v>
       </c>
       <c r="B30" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136859477</v>
       </c>
       <c r="B31" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>136859433</v>
       </c>
       <c r="B32" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>136860271</v>
       </c>
       <c r="B33" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136859496</v>
       </c>
       <c r="B34" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>136859497</v>
       </c>
       <c r="B35" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>136859556</v>
       </c>
       <c r="B36" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>136860254</v>
       </c>
       <c r="B37" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136859440</v>
       </c>
       <c r="B38" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>136859451</v>
       </c>
       <c r="B39" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>136859452</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>136859457</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>136859459</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>136859461</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>136859463</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>136859466</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136859468</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>136859470</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>136859475</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>136859484</v>
       </c>
       <c r="B49" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>136859486</v>
       </c>
       <c r="B50" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>136859488</v>
       </c>
       <c r="B51" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136859490</v>
       </c>
       <c r="B52" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136859491</v>
       </c>
       <c r="B53" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>136859493</v>
       </c>
       <c r="B54" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>136859494</v>
       </c>
       <c r="B55" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>136859495</v>
       </c>
       <c r="B56" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136859500</v>
       </c>
       <c r="B57" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>136859502</v>
       </c>
       <c r="B58" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>136859505</v>
       </c>
       <c r="B59" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136859507</v>
       </c>
       <c r="B60" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>136859513</v>
       </c>
       <c r="B61" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>136859518</v>
       </c>
       <c r="B62" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136859519</v>
       </c>
       <c r="B63" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>136859526</v>
       </c>
       <c r="B64" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>136859534</v>
       </c>
       <c r="B65" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>136859535</v>
       </c>
       <c r="B66" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>136859537</v>
       </c>
       <c r="B67" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>136859538</v>
       </c>
       <c r="B68" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>136859541</v>
       </c>
       <c r="B69" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>136859548</v>
       </c>
       <c r="B70" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136859551</v>
       </c>
       <c r="B71" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>136859553</v>
       </c>
       <c r="B72" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136859554</v>
       </c>
       <c r="B73" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>136859557</v>
       </c>
       <c r="B74" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136859562</v>
       </c>
       <c r="B75" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136859564</v>
       </c>
       <c r="B76" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>136859567</v>
       </c>
       <c r="B77" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136859572</v>
       </c>
       <c r="B78" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136859573</v>
       </c>
       <c r="B79" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136859577</v>
       </c>
       <c r="B80" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>136859580</v>
       </c>
       <c r="B81" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>136859583</v>
       </c>
       <c r="B82" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>136859587</v>
       </c>
       <c r="B83" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>136859589</v>
       </c>
       <c r="B84" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136859593</v>
       </c>
       <c r="B85" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>136859594</v>
       </c>
       <c r="B86" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136859595</v>
       </c>
       <c r="B87" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136859596</v>
       </c>
       <c r="B88" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136860249</v>
       </c>
       <c r="B89" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>136860250</v>
       </c>
       <c r="B90" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>136860262</v>
       </c>
       <c r="B91" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>136860264</v>
       </c>
       <c r="B92" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>136860266</v>
       </c>
       <c r="B93" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>136860267</v>
       </c>
       <c r="B94" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136860269</v>
       </c>
       <c r="B95" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>136860272</v>
       </c>
       <c r="B96" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>136860273</v>
       </c>
       <c r="B97" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>136860274</v>
       </c>
       <c r="B98" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>136860276</v>
       </c>
       <c r="B99" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136860281</v>
       </c>
       <c r="B100" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>136860282</v>
       </c>
       <c r="B101" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>136860287</v>
       </c>
       <c r="B102" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>136860289</v>
       </c>
       <c r="B103" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>136860292</v>
       </c>
       <c r="B104" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136860293</v>
       </c>
       <c r="B105" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>136860294</v>
       </c>
       <c r="B106" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136859455</v>
       </c>
       <c r="B107" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>136859445</v>
       </c>
       <c r="B108" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>136860263</v>
       </c>
       <c r="B109" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>136859435</v>
       </c>
       <c r="B110" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>136859448</v>
       </c>
       <c r="B111" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>136859449</v>
       </c>
       <c r="B112" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>136859506</v>
       </c>
       <c r="B113" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>136859522</v>
       </c>
       <c r="B114" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>136860247</v>
       </c>
       <c r="B115" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>136860248</v>
       </c>
       <c r="B116" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>136859443</v>
       </c>
       <c r="B117" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>136859479</v>
       </c>
       <c r="B118" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>136859528</v>
       </c>
       <c r="B171" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>136860284</v>
       </c>
       <c r="B172" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>136859579</v>
       </c>
       <c r="B173" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>136859527</v>
       </c>
       <c r="B174" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>136859515</v>
       </c>
       <c r="B175" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>136859531</v>
       </c>
       <c r="B176" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>136859586</v>
       </c>
       <c r="B177" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>136860255</v>
       </c>
       <c r="B178" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>136860258</v>
       </c>
       <c r="B179" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>136860270</v>
       </c>
       <c r="B180" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>136859480</v>
       </c>
       <c r="B181" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>136860261</v>
       </c>
       <c r="B182" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
